--- a/artfynd/A 12714-2026 artfynd.xlsx
+++ b/artfynd/A 12714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>345628</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557913.6746440418</v>
+        <v>557914</v>
       </c>
       <c r="R2" t="n">
-        <v>7315984.191597166</v>
+        <v>7315984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101196802</v>
+        <v>125581655</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,37 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ammarnäs, Ly lm</t>
+          <t>Bissandbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558095.9958805264</v>
+        <v>557905</v>
       </c>
       <c r="R3" t="n">
-        <v>7315796.539257468</v>
+        <v>7315970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Unga exemplar</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,51 +861,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125581666</v>
+        <v>125581658</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558003</v>
+        <v>558100</v>
       </c>
       <c r="R4" t="n">
-        <v>7315930</v>
+        <v>7315823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125581655</v>
+        <v>125581670</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>80367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557905</v>
+        <v>558101</v>
       </c>
       <c r="R5" t="n">
-        <v>7315970</v>
+        <v>7315816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1055,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,7 +1077,7 @@
         <v>125581675</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,201 +1173,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125581670</v>
-      </c>
-      <c r="B7" t="n">
-        <v>80011</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6457</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dvärgtufs</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Scytinium teretiusculum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bissandbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>558101</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7315816</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125581658</v>
-      </c>
-      <c r="B8" t="n">
-        <v>79980</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bissandbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>558100</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7315823</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12714-2026 artfynd.xlsx
+++ b/artfynd/A 12714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125581655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125581658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125581670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,8 +1198,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125581675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>